--- a/artfynd/A 2637-2022 artfynd.xlsx
+++ b/artfynd/A 2637-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2637-2022 artfynd.xlsx
+++ b/artfynd/A 2637-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98956904</v>
+        <v>98639305</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,24 +715,24 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullspång, Haddån, Vg</t>
+          <t>Äldre granskog Haddån 1:10, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445483.8170766</v>
+        <v>445500</v>
       </c>
       <c r="R2" t="n">
-        <v>6540462.238996993</v>
+        <v>6540441</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,27 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tuvorna var lokaliserade på flera dellokaler inom en radie av ca 15 m (tillagt 11/3)</t>
+          <t>Uppskattningsvis 40-50 individer av knärot 20-40 m till vänster om en liten skogstig. Knärot återfanns på två växtlokaler, inom 50 m från varandra. På växtlokalen längre söderut återfanns vintergröna blad och på växtlokalen lite längre norrut återfanns vinterståndare.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,30 +784,30 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Främst granskog med lång kontinuitet. Flerskiktad med inslag av tall. Granen var mellan 120-170 år gammal. Granbarkborreangrepp längre norrut, men runt knäroten var det mindre angrepp. Ett kalhygge ca 70 m från växtlokalerna.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristina Jungbark</t>
+          <t>Mathilda Bertills</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristina Jungbark</t>
+          <t>Mathilda Bertills, Viveca Luc</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98639305</v>
+        <v>98956904</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,24 +844,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Äldre granskog Haddån 1:10, Vg</t>
+          <t>Gullspång, Haddån, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445500.540188604</v>
+        <v>445484</v>
       </c>
       <c r="R3" t="n">
-        <v>6540440.361070293</v>
+        <v>6540463</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,27 +885,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Uppskattningsvis 40-50 individer av knärot 20-40 m till vänster om en liten skogstig. Knärot återfanns på två växtlokaler, inom 50 m från varandra. På växtlokalen längre söderut återfanns vintergröna blad och på växtlokalen lite längre norrut återfanns vinterståndare.</t>
+          <t>Tuvorna var lokaliserade på flera dellokaler inom en radie av ca 15 m (tillagt 11/3)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,20 +913,15 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Främst granskog med lång kontinuitet. Flerskiktad med inslag av tall. Granen var mellan 120-170 år gammal. Granbarkborreangrepp längre norrut, men runt knäroten var det mindre angrepp. Ett kalhygge ca 70 m från växtlokalerna.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mathilda Bertills</t>
+          <t>Kristina Jungbark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mathilda Bertills, Viveca Luc</t>
+          <t>Kristina Jungbark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
